--- a/reports/二级子公司C_利润表_2025-06.xlsx
+++ b/reports/二级子公司C_利润表_2025-06.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>90625773</v>
+        <v>92854933</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>87992523</v>
+        <v>88184846</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>498877913</v>
+        <v>497540966</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>412162</v>
+        <v>412639</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2324726</v>
+        <v>2330786</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>361515</v>
+        <v>360153</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2034040</v>
+        <v>2039932</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>310465</v>
+        <v>307978</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1743826</v>
+        <v>1748493</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>290082</v>
+        <v>286938</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1628267</v>
+        <v>1631500</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>155411</v>
+        <v>153582</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>872783</v>
+        <v>873609</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>124209</v>
+        <v>122887</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>698658</v>
+        <v>698475</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>88971929</v>
+        <v>91210756</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>86338679</v>
+        <v>86540669</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>82251519</v>
+        <v>82389011</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>466282121</v>
+        <v>464964888</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1231067</v>
+        <v>1238891</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>6993538</v>
+        <v>6973767</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>819487</v>
+        <v>827625</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>4660779</v>
+        <v>4649905</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3071460</v>
+        <v>3107569</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>17468834</v>
+        <v>17443908</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>409748</v>
+        <v>414460</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2327759</v>
+        <v>2327132</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>307773</v>
+        <v>310609</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1744789</v>
+        <v>1746422</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>514085</v>
+        <v>516816</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>2906616</v>
+        <v>2912370</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>618451</v>
+        <v>618756</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3487015</v>
+        <v>3496341</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2583003</v>
+        <v>2571670</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>14529043</v>
+        <v>14571140</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>50247</v>
+        <v>49821</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>299624</v>
+        <v>300412</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1229522</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>6991782</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>819074</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>4658908</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>61578261</v>
+        <v>65841536</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>54813079</v>
+        <v>54674490</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>53579700</v>
+        <v>53438238</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>303046124</v>
+        <v>302313046</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1233379</v>
+        <v>1236252</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>6994244</v>
+        <v>6974275</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2065450</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>11623015</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>662247</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3720072</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>414383</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2326007</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>497331</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2792783</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>372665</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2095876</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>248003</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1398031</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>206184</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1165496</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>930144</v>
+        <v>925498</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5230549</v>
+        <v>5245658</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>724694</v>
+        <v>718226</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>4069313</v>
+        <v>4079631</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>621679</v>
+        <v>614664</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>3489639</v>
+        <v>3495697</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4661586</v>
+        <v>4607202</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>26187832</v>
+        <v>26204382</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>200902</v>
+        <v>204858</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1200286</v>
+        <v>1163934</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>350871</v>
+        <v>348561</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2101625</v>
+        <v>2099230</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>400012</v>
+        <v>348561</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2402813</v>
+        <v>2099230</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>49878</v>
+        <v>50027</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>300409</v>
+        <v>299629</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>180530</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1078514</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>362241</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2034503</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>120704</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>719318</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>90528</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>539754</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>150726</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>900106</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>516523</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2912753</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>80045</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>480532</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>59883</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>360483</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>99590</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>600809</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>69612</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>420468</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>49700</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>300205</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>39784</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>240032</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>29884</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>179921</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>27393668</v>
+        <v>26627984</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>32084532</v>
+        <v>30016359</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>206666</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1162332</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>50251</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>299626</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>79527</v>
+        <v>80474</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>480243</v>
+        <v>479573</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>27314141</v>
+        <v>26754176</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2791152</v>
+        <v>2812969</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>16789527</v>
+        <v>16803288</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24522989</v>
+        <v>23941207</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24522989</v>
+        <v>23941207</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24522989</v>
+        <v>23941207</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24522989</v>
+        <v>23941207</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24522989</v>
+        <v>23941207</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
